--- a/jpcore-r4/feature/swg2_diagnosticreport-radiology/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/feature/swg2_diagnosticreport-radiology/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3828" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3830" uniqueCount="564">
   <si>
     <t>Property</t>
   </si>
@@ -650,7 +650,10 @@
     <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
+    <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -672,7 +675,10 @@
     <t>このObservationに関する分類（JP_SimpleObservationCategory_VS）、必須項目</t>
   </si>
   <si>
-    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
+    <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
     <t>Observation.category:first.id</t>
@@ -927,10 +933,10 @@
     <t>second</t>
   </si>
   <si>
-    <t>このObservationに関するLOINC上の分類、必須項目</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationDentalCategory_VS</t>
+    <t>第2カテゴリはLOINCのコードLP89803-8固定とする、ValueSetのバインディングを指定していないことに注意すること</t>
+  </si>
+  <si>
+    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
     <t>Observation.category:second.id</t>
@@ -3994,15 +4000,17 @@
       <c r="X16" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Y16" s="2"/>
+      <c r="Y16" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="Z16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
@@ -4036,10 +4044,10 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>83</v>
@@ -4047,13 +4055,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>83</v>
@@ -4063,7 +4071,7 @@
         <v>94</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>83</v>
@@ -4078,13 +4086,13 @@
         <v>198</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O17" t="s" s="2">
         <v>201</v>
@@ -4116,7 +4124,7 @@
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>83</v>
@@ -4158,10 +4166,10 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>83</v>
@@ -4169,10 +4177,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4195,13 +4203,13 @@
         <v>83</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4252,7 +4260,7 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4276,7 +4284,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4287,10 +4295,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4316,10 +4324,10 @@
         <v>139</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>156</v>
@@ -4363,7 +4371,7 @@
         <v>142</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>83</v>
@@ -4372,7 +4380,7 @@
         <v>143</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4396,7 +4404,7 @@
         <v>83</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4407,10 +4415,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4433,19 +4441,19 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>83</v>
@@ -4494,7 +4502,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4515,10 +4523,10 @@
         <v>83</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4529,10 +4537,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4555,13 +4563,13 @@
         <v>83</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4612,7 +4620,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4636,7 +4644,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4647,10 +4655,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4676,10 +4684,10 @@
         <v>139</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>156</v>
@@ -4723,7 +4731,7 @@
         <v>142</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>83</v>
@@ -4732,7 +4740,7 @@
         <v>143</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4756,7 +4764,7 @@
         <v>83</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4767,10 +4775,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4796,23 +4804,23 @@
         <v>108</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>83</v>
@@ -4854,7 +4862,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4875,10 +4883,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4889,10 +4897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4915,16 +4923,16 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4974,7 +4982,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4995,10 +5003,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -5009,10 +5017,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5038,21 +5046,21 @@
         <v>114</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>83</v>
@@ -5094,7 +5102,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5115,10 +5123,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5129,10 +5137,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5155,17 +5163,17 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5214,7 +5222,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5235,10 +5243,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5249,10 +5257,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5275,19 +5283,19 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5336,7 +5344,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5357,10 +5365,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5371,10 +5379,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5397,19 +5405,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5458,7 +5466,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5479,10 +5487,10 @@
         <v>83</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>83</v>
@@ -5493,13 +5501,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>83</v>
@@ -5524,13 +5532,13 @@
         <v>198</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>209</v>
+        <v>296</v>
       </c>
       <c r="O29" t="s" s="2">
         <v>201</v>
@@ -5558,11 +5566,13 @@
         <v>83</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y29" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>294</v>
+        <v>203</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>83</v>
@@ -5604,10 +5614,10 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>83</v>
@@ -5615,10 +5625,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5641,13 +5651,13 @@
         <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5698,7 +5708,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5722,7 +5732,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5733,10 +5743,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5762,10 +5772,10 @@
         <v>139</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>156</v>
@@ -5809,7 +5819,7 @@
         <v>142</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>83</v>
@@ -5818,7 +5828,7 @@
         <v>143</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5842,7 +5852,7 @@
         <v>83</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5853,10 +5863,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5879,19 +5889,19 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>83</v>
@@ -5940,7 +5950,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5961,10 +5971,10 @@
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -5975,10 +5985,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6001,13 +6011,13 @@
         <v>83</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6058,7 +6068,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6082,7 +6092,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6093,10 +6103,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6122,10 +6132,10 @@
         <v>139</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>156</v>
@@ -6169,7 +6179,7 @@
         <v>142</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>83</v>
@@ -6178,7 +6188,7 @@
         <v>143</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6202,7 +6212,7 @@
         <v>83</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6213,10 +6223,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6242,23 +6252,23 @@
         <v>108</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>83</v>
@@ -6300,7 +6310,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6321,10 +6331,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6335,10 +6345,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6361,16 +6371,16 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6420,7 +6430,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6441,10 +6451,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6455,10 +6465,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6484,21 +6494,21 @@
         <v>114</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>83</v>
@@ -6540,7 +6550,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6561,10 +6571,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6575,10 +6585,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6601,17 +6611,17 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6660,7 +6670,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6681,10 +6691,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6695,10 +6705,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6721,19 +6731,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6782,7 +6792,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6803,10 +6813,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6817,10 +6827,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6843,19 +6853,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6904,7 +6914,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6925,10 +6935,10 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
@@ -6939,13 +6949,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>83</v>
@@ -6970,13 +6980,13 @@
         <v>198</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>209</v>
+        <v>296</v>
       </c>
       <c r="O41" t="s" s="2">
         <v>201</v>
@@ -7008,7 +7018,7 @@
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>83</v>
@@ -7050,10 +7060,10 @@
         <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -7061,10 +7071,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7087,13 +7097,13 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7144,7 +7154,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7168,7 +7178,7 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7179,10 +7189,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7208,10 +7218,10 @@
         <v>139</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>156</v>
@@ -7255,7 +7265,7 @@
         <v>142</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>83</v>
@@ -7264,7 +7274,7 @@
         <v>143</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7288,7 +7298,7 @@
         <v>83</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7299,10 +7309,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7325,19 +7335,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7386,7 +7396,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7407,10 +7417,10 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7421,10 +7431,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7447,13 +7457,13 @@
         <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7504,7 +7514,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7528,7 +7538,7 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7539,10 +7549,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7568,10 +7578,10 @@
         <v>139</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>156</v>
@@ -7615,7 +7625,7 @@
         <v>142</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>83</v>
@@ -7624,7 +7634,7 @@
         <v>143</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7648,7 +7658,7 @@
         <v>83</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7659,10 +7669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7688,23 +7698,23 @@
         <v>108</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>83</v>
@@ -7746,7 +7756,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7767,10 +7777,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7781,10 +7791,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7807,16 +7817,16 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7866,7 +7876,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7887,10 +7897,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7901,10 +7911,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7930,21 +7940,21 @@
         <v>114</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>83</v>
@@ -7986,7 +7996,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8007,10 +8017,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8021,10 +8031,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8047,17 +8057,17 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8106,7 +8116,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8127,10 +8137,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8141,10 +8151,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8167,19 +8177,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8228,7 +8238,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8249,10 +8259,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8263,10 +8273,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8289,19 +8299,19 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8350,7 +8360,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8371,10 +8381,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8385,14 +8395,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8414,16 +8424,16 @@
         <v>198</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8448,13 +8458,13 @@
         <v>83</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>83</v>
@@ -8472,7 +8482,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>94</v>
@@ -8487,30 +8497,30 @@
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8533,13 +8543,13 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8590,7 +8600,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8614,7 +8624,7 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8625,10 +8635,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8654,10 +8664,10 @@
         <v>139</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>156</v>
@@ -8701,7 +8711,7 @@
         <v>142</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>83</v>
@@ -8710,7 +8720,7 @@
         <v>143</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8734,7 +8744,7 @@
         <v>83</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8745,10 +8755,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8771,19 +8781,19 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8832,7 +8842,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8853,10 +8863,10 @@
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8867,10 +8877,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8893,13 +8903,13 @@
         <v>83</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8950,7 +8960,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8974,7 +8984,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -8985,10 +8995,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9014,10 +9024,10 @@
         <v>139</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>156</v>
@@ -9061,7 +9071,7 @@
         <v>142</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>83</v>
@@ -9070,7 +9080,7 @@
         <v>143</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9094,7 +9104,7 @@
         <v>83</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -9105,10 +9115,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9134,23 +9144,23 @@
         <v>108</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>83</v>
@@ -9192,7 +9202,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9213,10 +9223,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9227,10 +9237,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9253,16 +9263,16 @@
         <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9312,7 +9322,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9333,10 +9343,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9347,10 +9357,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9376,21 +9386,21 @@
         <v>114</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="S61" t="s" s="2">
         <v>83</v>
@@ -9432,7 +9442,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9453,10 +9463,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9467,10 +9477,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9493,17 +9503,17 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9513,7 +9523,7 @@
         <v>83</v>
       </c>
       <c r="S62" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="T62" t="s" s="2">
         <v>83</v>
@@ -9552,7 +9562,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9573,10 +9583,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9587,10 +9597,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9613,19 +9623,19 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9674,7 +9684,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9695,10 +9705,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9709,10 +9719,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9735,19 +9745,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9796,7 +9806,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9817,10 +9827,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9831,10 +9841,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9857,19 +9867,19 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -9918,7 +9928,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9933,19 +9943,19 @@
         <v>106</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -9953,10 +9963,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9979,7 +9989,7 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L66" t="s" s="2">
         <v>179</v>
@@ -9988,7 +9998,7 @@
         <v>179</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10038,7 +10048,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10059,13 +10069,13 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10073,14 +10083,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10099,19 +10109,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10160,7 +10170,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10175,19 +10185,19 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10195,14 +10205,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10221,19 +10231,19 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10282,7 +10292,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10297,19 +10307,19 @@
         <v>106</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10317,10 +10327,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10343,16 +10353,16 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10402,7 +10412,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10423,13 +10433,13 @@
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -10437,10 +10447,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10463,19 +10473,19 @@
         <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10524,7 +10534,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10539,19 +10549,19 @@
         <v>106</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>83</v>
@@ -10559,10 +10569,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10588,16 +10598,16 @@
         <v>198</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10626,7 +10636,7 @@
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10644,7 +10654,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10653,7 +10663,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -10662,27 +10672,27 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10708,16 +10718,16 @@
         <v>198</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10742,13 +10752,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10766,7 +10776,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10775,7 +10785,7 @@
         <v>94</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>106</v>
@@ -10790,7 +10800,7 @@
         <v>137</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
@@ -10801,14 +10811,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10836,10 +10846,10 @@
         <v>179</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -10864,13 +10874,13 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
@@ -10888,7 +10898,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10906,27 +10916,27 @@
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10949,7 +10959,7 @@
         <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L74" t="s" s="2">
         <v>179</v>
@@ -10958,10 +10968,10 @@
         <v>179</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11010,7 +11020,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11031,10 +11041,10 @@
         <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
@@ -11045,10 +11055,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11074,13 +11084,13 @@
         <v>198</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11110,7 +11120,7 @@
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11128,7 +11138,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11146,27 +11156,27 @@
         <v>83</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11192,16 +11202,16 @@
         <v>198</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>83</v>
@@ -11226,13 +11236,13 @@
         <v>83</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>83</v>
@@ -11250,7 +11260,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11271,10 +11281,10 @@
         <v>83</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11285,10 +11295,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11311,7 +11321,7 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>179</v>
@@ -11320,7 +11330,7 @@
         <v>179</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11370,7 +11380,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11388,27 +11398,27 @@
         <v>83</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11431,16 +11441,16 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11490,7 +11500,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11508,27 +11518,27 @@
         <v>83</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11551,7 +11561,7 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="L79" t="s" s="2">
         <v>179</v>
@@ -11560,10 +11570,10 @@
         <v>179</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
@@ -11612,7 +11622,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11624,7 +11634,7 @@
         <v>83</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>83</v>
@@ -11633,10 +11643,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11647,10 +11657,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11673,13 +11683,13 @@
         <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11730,7 +11740,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -11754,7 +11764,7 @@
         <v>83</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -11765,10 +11775,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11794,10 +11804,10 @@
         <v>139</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>156</v>
@@ -11850,7 +11860,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -11874,7 +11884,7 @@
         <v>83</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -11885,14 +11895,14 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11914,10 +11924,10 @@
         <v>139</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>156</v>
@@ -11972,7 +11982,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12007,10 +12017,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12033,13 +12043,13 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12090,7 +12100,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12099,7 +12109,7 @@
         <v>94</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>106</v>
@@ -12111,10 +12121,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12125,10 +12135,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12151,13 +12161,13 @@
         <v>83</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12208,7 +12218,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12217,7 +12227,7 @@
         <v>94</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>106</v>
@@ -12229,10 +12239,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12243,10 +12253,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12272,16 +12282,16 @@
         <v>198</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12309,10 +12319,10 @@
         <v>118</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>83</v>
@@ -12330,7 +12340,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12348,13 +12358,13 @@
         <v>83</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12365,10 +12375,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12394,16 +12404,16 @@
         <v>198</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12428,13 +12438,13 @@
         <v>83</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>83</v>
@@ -12452,7 +12462,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12470,13 +12480,13 @@
         <v>83</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12487,10 +12497,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12513,17 +12523,17 @@
         <v>83</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
@@ -12572,7 +12582,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12596,7 +12606,7 @@
         <v>83</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12607,10 +12617,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12633,13 +12643,13 @@
         <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12690,7 +12700,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12711,10 +12721,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12725,10 +12735,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12751,16 +12761,16 @@
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12810,7 +12820,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12831,10 +12841,10 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -12845,10 +12855,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12871,7 +12881,7 @@
         <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>179</v>
@@ -12880,7 +12890,7 @@
         <v>179</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12930,7 +12940,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -12951,10 +12961,10 @@
         <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -12965,10 +12975,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12991,7 +13001,7 @@
         <v>95</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="L91" t="s" s="2">
         <v>179</v>
@@ -13000,10 +13010,10 @@
         <v>179</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13052,7 +13062,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13073,10 +13083,10 @@
         <v>83</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
@@ -13087,10 +13097,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13113,13 +13123,13 @@
         <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13170,7 +13180,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13194,7 +13204,7 @@
         <v>83</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13205,10 +13215,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13234,10 +13244,10 @@
         <v>139</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>156</v>
@@ -13290,7 +13300,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13314,7 +13324,7 @@
         <v>83</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
@@ -13325,14 +13335,14 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13354,10 +13364,10 @@
         <v>139</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>156</v>
@@ -13412,7 +13422,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13447,10 +13457,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13476,16 +13486,16 @@
         <v>198</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13510,13 +13520,13 @@
         <v>83</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>83</v>
@@ -13534,7 +13544,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>94</v>
@@ -13552,16 +13562,16 @@
         <v>83</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>83</v>
@@ -13569,10 +13579,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13595,19 +13605,19 @@
         <v>95</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -13656,7 +13666,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13674,27 +13684,27 @@
         <v>83</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13720,16 +13730,16 @@
         <v>198</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -13754,13 +13764,13 @@
         <v>83</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>83</v>
@@ -13778,7 +13788,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13787,7 +13797,7 @@
         <v>94</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>106</v>
@@ -13802,7 +13812,7 @@
         <v>137</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
@@ -13813,14 +13823,14 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13842,16 +13852,16 @@
         <v>198</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -13876,13 +13886,13 @@
         <v>83</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>83</v>
@@ -13900,7 +13910,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -13918,27 +13928,27 @@
         <v>83</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13964,16 +13974,16 @@
         <v>84</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>83</v>
@@ -14022,7 +14032,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14043,10 +14053,10 @@
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>83</v>
